--- a/jogos_2024-11-18.xlsx
+++ b/jogos_2024-11-18.xlsx
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.95</v>
       </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AD7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>3.1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45614.80208333334</v>
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="O8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.63</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45614.80208333334</v>
